--- a/frontend/e2e/testdata/План подготовительного участка.xlsx
+++ b/frontend/e2e/testdata/План подготовительного участка.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:F7"/>
+  <dimension ref="A4:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -439,10 +439,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Длина, м</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Кол-во, шт</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -470,6 +475,9 @@
         </is>
       </c>
       <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
         <v>300</v>
       </c>
     </row>
@@ -495,6 +503,9 @@
         </is>
       </c>
       <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
         <v>200</v>
       </c>
     </row>
@@ -514,8 +525,10 @@
           <t>серебро</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
         <v>100</v>
       </c>
     </row>
